--- a/error_models/conv_models/nv_32x8_b1_dat-2097152_wt-131072_int32/unique_complete_df.xlsx
+++ b/error_models/conv_models/nv_32x8_b1_dat-2097152_wt-131072_int32/unique_complete_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:AT40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,136 @@
           <t>Skip4</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>skip_4-single</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>skip_4-multi</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_alternated_blocks-single</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_alternated_blocks-multi</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_wake-single</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_wake-multi</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>quasi_shattered_channel-single</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>quasi_shattered_channel-multi</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_random-single</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_random-multi</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>single_block-single</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>single_block-multi</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>same_row-single</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>same_row-multi</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>full_channels-single</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>full_channels-multi</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>multi_channel_block-single</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>multi_channel_block-multi</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>shattered_channel-single</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>shattered_channel-multi</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>multiple_channels_uncategorized-single</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>multiple_channels_uncategorized-multi</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rectangles-single</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>rectangles-multi</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>single-single</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>single-multi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -552,16 +682,16 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9966613301954934</v>
+        <v>0.9970608807899808</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0033291461065111</v>
+        <v>0.0029315086179794</v>
       </c>
       <c r="I2" t="n">
-        <v>9.465959628089704e-06</v>
+        <v>7.552853672781481e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4648636072535089</v>
+        <v>0.4648636072535088</v>
       </c>
       <c r="K2" t="n">
         <v>0.0934548218002085</v>
@@ -591,6 +721,84 @@
         <v>2.668988859357488e-05</v>
       </c>
       <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.0601436519584357</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.9398563480415644</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -616,19 +824,19 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9956043249506056</v>
+        <v>0.9958084185929682</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0043853409499029</v>
+        <v>0.0041830522140877</v>
       </c>
       <c r="I3" t="n">
-        <v>1.027636112426157e-05</v>
+        <v>8.471454576859035e-06</v>
       </c>
       <c r="J3" t="n">
         <v>0.1124122374316609</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3886565158249143</v>
+        <v>0.3886565158249144</v>
       </c>
       <c r="L3" t="n">
         <v>0.2253109204430345</v>
@@ -656,6 +864,84 @@
       </c>
       <c r="T3" t="n">
         <v>0.0002142284678489</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.9993626513702996</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.0006373486297004</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.0601435918536246</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.9398564081463754</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -680,13 +966,13 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9986892350809492</v>
+        <v>0.9987813375700154</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0012999383977284</v>
+        <v>0.001209383284565</v>
       </c>
       <c r="I4" t="n">
-        <v>1.076878295490068e-05</v>
+        <v>9.221407052341847e-06</v>
       </c>
       <c r="J4" t="n">
         <v>0.050463527273402</v>
@@ -707,7 +993,7 @@
         <v>0.0660520956573491</v>
       </c>
       <c r="P4" t="n">
-        <v>2.428215122952812e-06</v>
+        <v>2.428215122952811e-06</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0220196774140313</v>
@@ -720,6 +1006,84 @@
       </c>
       <c r="T4" t="n">
         <v>4.147517436196904e-07</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.999663466259394</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.0003365337406058</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.0601436768804276</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.9398563231195722</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -744,19 +1108,19 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9977842006720646</v>
+        <v>0.9978545984675528</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0022047709994993</v>
+        <v>0.0021358992802787</v>
       </c>
       <c r="I5" t="n">
-        <v>1.097059006879596e-05</v>
+        <v>9.444513801073507e-06</v>
       </c>
       <c r="J5" t="n">
         <v>0.0541223292968715</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4551586710038119</v>
+        <v>0.455158671003812</v>
       </c>
       <c r="L5" t="n">
         <v>0.1800080590935711</v>
@@ -784,6 +1148,84 @@
       </c>
       <c r="T5" t="n">
         <v>0.0015695130975847</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.9996603213430532</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.0003396786569467</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.0601436685408916</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.9398563314591084</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -808,13 +1250,13 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9986152551314278</v>
+        <v>0.9986600446913748</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0013737672308309</v>
+        <v>0.0013305179158152</v>
       </c>
       <c r="I6" t="n">
-        <v>1.091989937393553e-05</v>
+        <v>9.379654442472182e-06</v>
       </c>
       <c r="J6" t="n">
         <v>0.0340085967316777</v>
@@ -848,6 +1290,84 @@
       </c>
       <c r="T6" t="n">
         <v>0.0012590041884596</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.9994935822724006</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.0005064177275993</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.0601681476563645</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.9398318523436354</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -872,13 +1392,13 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9977015598461756</v>
+        <v>0.9982699913705976</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0022877544040582</v>
+        <v>0.0017211104156602</v>
       </c>
       <c r="I7" t="n">
-        <v>1.062801139886548e-05</v>
+        <v>8.840475374939127e-06</v>
       </c>
       <c r="J7" t="n">
         <v>0.4470138861534021</v>
@@ -912,6 +1432,84 @@
       </c>
       <c r="T7" t="n">
         <v>7.534166424233711e-07</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.0601437021892878</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.939856297810712</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -936,13 +1534,13 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9964776178060764</v>
+        <v>0.9970977859612548</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0035113773673532</v>
+        <v>0.0028930214202267</v>
       </c>
       <c r="I8" t="n">
-        <v>1.094708820309203e-05</v>
+        <v>9.134880151049476e-06</v>
       </c>
       <c r="J8" t="n">
         <v>0.1255357329358054</v>
@@ -963,7 +1561,7 @@
         <v>0.07597901067714639</v>
       </c>
       <c r="P8" t="n">
-        <v>4.253559696359572e-06</v>
+        <v>4.253559696359573e-06</v>
       </c>
       <c r="Q8" t="n">
         <v>0.0666042674777126</v>
@@ -976,6 +1574,84 @@
       </c>
       <c r="T8" t="n">
         <v>0.0100835246752953</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.0601436574782959</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.939856342521704</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1000,13 +1676,13 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9980214859137058</v>
+        <v>0.9990668387669625</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0019665868692391</v>
+        <v>0.0009228714420521</v>
       </c>
       <c r="I9" t="n">
-        <v>1.18694786878295e-05</v>
+        <v>1.023205261822674e-05</v>
       </c>
       <c r="J9" t="n">
         <v>0.2947113784351706</v>
@@ -1027,10 +1703,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>7.612274742402023e-06</v>
+        <v>7.612274742402022e-06</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4510592844228339</v>
+        <v>0.451059284422834</v>
       </c>
       <c r="R9" t="n">
         <v>2.210179672393788e-05</v>
@@ -1040,6 +1716,84 @@
       </c>
       <c r="T9" t="n">
         <v>1.29797505415866e-05</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1064,19 +1818,19 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9992098688427874</v>
+        <v>0.999313614435163</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0007791244221983</v>
+        <v>0.0006767087781422</v>
       </c>
       <c r="I10" t="n">
-        <v>1.094899664697781e-05</v>
+        <v>9.619048327502796e-06</v>
       </c>
       <c r="J10" t="n">
         <v>0.0298173449191854</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6943142479215996</v>
+        <v>0.6943142479215995</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1103,6 +1857,84 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1128,19 +1960,19 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9996413589597436</v>
+        <v>0.9997664361131036</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0003479754316467</v>
+        <v>0.000224725320906</v>
       </c>
       <c r="I11" t="n">
-        <v>1.060787024221307e-05</v>
+        <v>8.780827622820686e-06</v>
       </c>
       <c r="J11" t="n">
         <v>0.0002227903915923</v>
       </c>
       <c r="K11" t="n">
-        <v>0.757430524533685</v>
+        <v>0.7574305245336851</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1149,7 +1981,7 @@
         <v>2.323273162441621e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>0.09689928740602841</v>
+        <v>0.09689928740602829</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1167,6 +1999,84 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1192,13 +2102,13 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9982330460073732</v>
+        <v>0.9987654669291792</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0017552912177563</v>
+        <v>0.0012243180101789</v>
       </c>
       <c r="I12" t="n">
-        <v>1.160503650334686e-05</v>
+        <v>1.015732227458142e-05</v>
       </c>
       <c r="J12" t="n">
         <v>0.1430071878886577</v>
@@ -1232,6 +2142,84 @@
       </c>
       <c r="T12" t="n">
         <v>0.0016168451585859</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1256,13 +2244,13 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9993731881292</v>
+        <v>0.9997204261302196</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0006155531490127</v>
+        <v>0.0002700638715348</v>
       </c>
       <c r="I13" t="n">
-        <v>1.120098342007878e-05</v>
+        <v>9.452259878412959e-06</v>
       </c>
       <c r="J13" t="n">
         <v>0.0728795669553698</v>
@@ -1296,6 +2284,84 @@
       </c>
       <c r="T13" t="n">
         <v>5.78094704851046e-06</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1320,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9980239881492632</v>
+        <v>0.9984088207119576</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001964239029968</v>
+        <v>0.0015807185049269</v>
       </c>
       <c r="I14" t="n">
-        <v>1.171508240154161e-05</v>
+        <v>1.04030447482993e-05</v>
       </c>
       <c r="J14" t="n">
         <v>0.0411196101622397</v>
@@ -1360,6 +2426,84 @@
       </c>
       <c r="T14" t="n">
         <v>1.589083575221068e-05</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1384,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9995133891702273</v>
+        <v>0.999783363530822</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0004748252359999</v>
+        <v>0.0002066441911791</v>
       </c>
       <c r="I15" t="n">
-        <v>1.172785540570306e-05</v>
+        <v>9.934539631584196e-06</v>
       </c>
       <c r="J15" t="n">
         <v>0.1213874853371758</v>
@@ -1424,6 +2568,84 @@
       </c>
       <c r="T15" t="n">
         <v>6.177143541326481e-06</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1448,13 +2670,13 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9997641276535688</v>
+        <v>0.9999035124624248</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0002248873232143</v>
+        <v>8.75422575093377e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>1.092728484966902e-05</v>
+        <v>8.88754169859135e-06</v>
       </c>
       <c r="J16" t="n">
         <v>0.0486491909560327</v>
@@ -1475,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8853264896345084</v>
+        <v>0.8853264896345083</v>
       </c>
       <c r="Q16" t="n">
         <v>0.0485760521944168</v>
@@ -1488,6 +2710,84 @@
       </c>
       <c r="T16" t="n">
         <v>6.673150147527908e-06</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1512,13 +2812,13 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9988341426448688</v>
+        <v>0.9990745967760062</v>
       </c>
       <c r="H17" t="n">
-        <v>0.001154283754539</v>
+        <v>0.0009152389484001</v>
       </c>
       <c r="I17" t="n">
-        <v>1.151586222519802e-05</v>
+        <v>1.010653722632491e-05</v>
       </c>
       <c r="J17" t="n">
         <v>0.0523884603054125</v>
@@ -1533,7 +2833,7 @@
         <v>0.016190434629397</v>
       </c>
       <c r="N17" t="n">
-        <v>9.154790825230075e-06</v>
+        <v>9.154790825230074e-06</v>
       </c>
       <c r="O17" t="n">
         <v>5.721966221132586e-09</v>
@@ -1552,6 +2852,84 @@
       </c>
       <c r="T17" t="n">
         <v>0.0023427675199765</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1576,13 +2954,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9996488160208898</v>
+        <v>0.9998530210218576</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0003399440703641</v>
+        <v>0.0001377829422603</v>
       </c>
       <c r="I18" t="n">
-        <v>1.118217037868728e-05</v>
+        <v>9.138297514923172e-06</v>
       </c>
       <c r="J18" t="n">
         <v>0.0244116404317717</v>
@@ -1603,7 +2981,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7724074120940128</v>
+        <v>0.7724074120940126</v>
       </c>
       <c r="Q18" t="n">
         <v>0.1938961639766374</v>
@@ -1616,6 +2994,84 @@
       </c>
       <c r="T18" t="n">
         <v>1.222965435045942e-05</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1640,19 +3096,19 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9996570009613792</v>
+        <v>0.9997373751990491</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0003320571185186</v>
+        <v>0.0002532161692565</v>
       </c>
       <c r="I19" t="n">
-        <v>1.088418173503831e-05</v>
+        <v>9.350893326923242e-06</v>
       </c>
       <c r="J19" t="n">
         <v>0.0016607488133891</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8927904366100771</v>
+        <v>0.892790436610077</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1679,6 +3135,84 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1704,13 +3238,13 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9997099495330248</v>
+        <v>0.9998337695445598</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0002795486987063</v>
+        <v>0.000157705143853</v>
       </c>
       <c r="I20" t="n">
-        <v>1.044402990153728e-05</v>
+        <v>8.467573219811256e-06</v>
       </c>
       <c r="J20" t="n">
         <v>0.0035609744190337</v>
@@ -1743,6 +3277,84 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1768,19 +3380,19 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9992799910418956</v>
+        <v>0.9993693428760536</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0007087428999239</v>
+        <v>0.0006207443097648</v>
       </c>
       <c r="I21" t="n">
-        <v>1.120831981329176e-05</v>
+        <v>9.855075814226207e-06</v>
       </c>
       <c r="J21" t="n">
         <v>0.0068405302047322</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7415270581602457</v>
+        <v>0.7415270581602458</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1807,6 +3419,84 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1832,13 +3522,13 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0879427422093534</v>
+        <v>0.4564744900633816</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9120452767904376</v>
+        <v>0.5435147420935058</v>
       </c>
       <c r="I22" t="n">
-        <v>1.192326184159092e-05</v>
+        <v>1.071010474527647e-05</v>
       </c>
       <c r="J22" t="n">
         <v>0.0010540686188921</v>
@@ -1871,6 +3561,84 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1896,19 +3664,19 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5334918486230102</v>
+        <v>0.5616201945443819</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4664964940185195</v>
+        <v>0.4383692522533035</v>
       </c>
       <c r="I23" t="n">
-        <v>1.159962010284802e-05</v>
+        <v>1.049546394736786e-05</v>
       </c>
       <c r="J23" t="n">
         <v>0.2814178060244685</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7155284001246498</v>
+        <v>0.7155284001246497</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1936,6 +3704,84 @@
       </c>
       <c r="T23" t="n">
         <v>4.010989368309911e-06</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1960,13 +3806,13 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9966130947440078</v>
+        <v>0.9970674086289752</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0033752019216364</v>
+        <v>0.0029221006881305</v>
       </c>
       <c r="I24" t="n">
-        <v>1.164559598853222e-05</v>
+        <v>1.043294452696141e-05</v>
       </c>
       <c r="J24" t="n">
         <v>0.042651307326255</v>
@@ -2000,6 +3846,84 @@
       </c>
       <c r="T24" t="n">
         <v>0.0013756183748347</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2024,13 +3948,13 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9978471393267028</v>
+        <v>0.9980202385980472</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0021410322420325</v>
+        <v>0.0019691327124607</v>
       </c>
       <c r="I25" t="n">
-        <v>1.177069289728159e-05</v>
+        <v>1.057095112492609e-05</v>
       </c>
       <c r="J25" t="n">
         <v>0.0169757817536677</v>
@@ -2064,6 +3988,84 @@
       </c>
       <c r="T25" t="n">
         <v>0.0026272654989634</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2088,13 +4090,13 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.998548788168254</v>
+        <v>0.9985867064411492</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0014400499815312</v>
+        <v>0.0014036324354832</v>
       </c>
       <c r="I26" t="n">
-        <v>1.110411184783084e-05</v>
+        <v>9.603385000067223e-06</v>
       </c>
       <c r="J26" t="n">
         <v>0.0267175018534994</v>
@@ -2128,6 +4130,84 @@
       </c>
       <c r="T26" t="n">
         <v>0.0508003363117567</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.9991002517197236</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.0008997482802761</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.0601437703608389</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0.9398562296391612</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2152,13 +4232,13 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9951568531059048</v>
+        <v>0.9956601312862088</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0048324640459724</v>
+        <v>0.0043309647984937</v>
       </c>
       <c r="I27" t="n">
-        <v>1.06251097557411e-05</v>
+        <v>8.846176930220794e-06</v>
       </c>
       <c r="J27" t="n">
         <v>0.1766009540074539</v>
@@ -2179,7 +4259,7 @@
         <v>0.0682205949987074</v>
       </c>
       <c r="P27" t="n">
-        <v>3.709299940487309e-06</v>
+        <v>3.70929994048731e-06</v>
       </c>
       <c r="Q27" t="n">
         <v>0.0342252344453126</v>
@@ -2192,6 +4272,84 @@
       </c>
       <c r="T27" t="n">
         <v>0.0210608290471515</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0.0601436798342393</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0.9398563201657608</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2216,13 +4374,13 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9975362829525152</v>
+        <v>0.9976654385627982</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0024530738407152</v>
+        <v>0.0023256186455008</v>
       </c>
       <c r="I28" t="n">
-        <v>1.058546840241002e-05</v>
+        <v>8.885053333630302e-06</v>
       </c>
       <c r="J28" t="n">
         <v>0.0490022766589829</v>
@@ -2243,7 +4401,7 @@
         <v>0.0880680331774318</v>
       </c>
       <c r="P28" t="n">
-        <v>0.4360487141219952</v>
+        <v>0.4360487141219951</v>
       </c>
       <c r="Q28" t="n">
         <v>0.0294052849518392</v>
@@ -2256,6 +4414,84 @@
       </c>
       <c r="T28" t="n">
         <v>0.0150773603444507</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2280,13 +4516,13 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9955282185499652</v>
+        <v>0.9956459757812586</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0044609277369961</v>
+        <v>0.0043448240344406</v>
       </c>
       <c r="I29" t="n">
-        <v>1.079597467126426e-05</v>
+        <v>9.142445933243638e-06</v>
       </c>
       <c r="J29" t="n">
         <v>0.0020976056137648</v>
@@ -2320,6 +4556,84 @@
       </c>
       <c r="T29" t="n">
         <v>0.02811592477762</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.0588223645662031</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.9411776354337968</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2344,13 +4658,13 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0925470910890529</v>
+        <v>0.4606602081376381</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9074418385181928</v>
+        <v>0.539329862301924</v>
       </c>
       <c r="I30" t="n">
-        <v>1.101265438712476e-05</v>
+        <v>9.87182207061686e-06</v>
       </c>
       <c r="J30" t="n">
         <v>0.0002689858061431</v>
@@ -2383,6 +4697,84 @@
         <v>5.048163266842828e-10</v>
       </c>
       <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2408,13 +4800,13 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9932774220365792</v>
+        <v>0.9947351703719656</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0067102887483409</v>
+        <v>0.005253846996312</v>
       </c>
       <c r="I31" t="n">
-        <v>1.223147671264015e-05</v>
+        <v>1.092489335516587e-05</v>
       </c>
       <c r="J31" t="n">
         <v>0.162184380919582</v>
@@ -2435,10 +4827,10 @@
         <v>1.375890722956771e-07</v>
       </c>
       <c r="P31" t="n">
-        <v>4.299995675016799e-06</v>
+        <v>4.2999956750168e-06</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.4208819039687842</v>
+        <v>0.4208819039687843</v>
       </c>
       <c r="R31" t="n">
         <v>1.806059206932854e-05</v>
@@ -2448,6 +4840,84 @@
       </c>
       <c r="T31" t="n">
         <v>1.304087402059125e-05</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2513,6 +4983,84 @@
       <c r="T32" t="n">
         <v>3.999282607512221e-07</v>
       </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -2536,13 +5084,13 @@
         <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5343475226292497</v>
+        <v>0.5394700223404187</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4656422638265908</v>
+        <v>0.4605216259256646</v>
       </c>
       <c r="I33" t="n">
-        <v>1.015580579226309e-05</v>
+        <v>8.293995549455326e-06</v>
       </c>
       <c r="J33" t="n">
         <v>0.2092905055481372</v>
@@ -2576,6 +5124,84 @@
       </c>
       <c r="T33" t="n">
         <v>0.0001248184384666</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2600,19 +5226,19 @@
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1525059010335975</v>
+        <v>0.3899910008940899</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8474838755624308</v>
+        <v>0.6100006531783309</v>
       </c>
       <c r="I34" t="n">
-        <v>1.016566560447181e-05</v>
+        <v>8.288189212092459e-06</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9959923245526224</v>
+        <v>0.9959923245526228</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2640,6 +5266,84 @@
       </c>
       <c r="T34" t="n">
         <v>0.0003036642823704</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2664,13 +5368,13 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9970505705665231</v>
+        <v>0.9977487239418743</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00293953783938675</v>
+        <v>0.00224321916395075</v>
       </c>
       <c r="I35" t="n">
-        <v>9.833855722776437e-06</v>
+        <v>7.999155807480883e-06</v>
       </c>
       <c r="J35" t="n">
         <v>0.2606754565978011</v>
@@ -2691,7 +5395,7 @@
         <v>0.08216708836778325</v>
       </c>
       <c r="P35" t="n">
-        <v>2.42834111826533e-06</v>
+        <v>2.428341118265331e-06</v>
       </c>
       <c r="Q35" t="n">
         <v>0.04787173368065545</v>
@@ -2704,6 +5408,84 @@
       </c>
       <c r="T35" t="n">
         <v>0.01729885781760712</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.0308187601353429</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0.969181239864657</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2728,13 +5510,13 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.09616493647071644</v>
+        <v>0.3780880368360491</v>
       </c>
       <c r="H36" t="n">
-        <v>0.903825154145862</v>
+        <v>0.6219037809836955</v>
       </c>
       <c r="I36" t="n">
-        <v>9.851645054173343e-06</v>
+        <v>8.12444188804311e-06</v>
       </c>
       <c r="J36" t="n">
         <v>0.0002692842159856</v>
@@ -2768,6 +5550,84 @@
       </c>
       <c r="T36" t="n">
         <v>1.107099283099145e-08</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2792,13 +5652,13 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9908465718560122</v>
+        <v>0.9913463127406167</v>
       </c>
       <c r="H37" t="n">
-        <v>0.009142687293317849</v>
+        <v>0.0086446721123025</v>
       </c>
       <c r="I37" t="n">
-        <v>1.068311230255426e-05</v>
+        <v>8.957408713475789e-06</v>
       </c>
       <c r="J37" t="n">
         <v>0.1644756318087491</v>
@@ -2832,6 +5692,84 @@
       </c>
       <c r="T37" t="n">
         <v>0.0067926380532664</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>6.91173154459638e-09</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0.9999999930882684</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2856,13 +5794,13 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.992884107976379</v>
+        <v>0.9930947811703106</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0071051429877192</v>
+        <v>0.006896132347495851</v>
       </c>
       <c r="I38" t="n">
-        <v>1.069129753465139e-05</v>
+        <v>9.028743826126227e-06</v>
       </c>
       <c r="J38" t="n">
         <v>0.07696419881105945</v>
@@ -2896,6 +5834,84 @@
       </c>
       <c r="T38" t="n">
         <v>0.00383033473021645</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.9994576959775634</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.0005423040224364</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2920,13 +5936,13 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9964039519204457</v>
+        <v>0.9965936541039709</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00358502572041875</v>
+        <v>0.003396805378778325</v>
       </c>
       <c r="I39" t="n">
-        <v>1.096462076813958e-05</v>
+        <v>9.482778883366627e-06</v>
       </c>
       <c r="J39" t="n">
         <v>0.02605461004909563</v>
@@ -2960,6 +5976,84 @@
       </c>
       <c r="T39" t="n">
         <v>0.00333015666035385</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.7494389442717997</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.00056105572820025</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.04510783172555782</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0.7048921682744422</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2984,19 +6078,19 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9985378275924628</v>
+        <v>0.9986247528817271</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0014511629773152</v>
+        <v>0.0013656784984827</v>
       </c>
       <c r="I40" t="n">
-        <v>1.095169185479533e-05</v>
+        <v>9.510881422999171e-06</v>
       </c>
       <c r="J40" t="n">
         <v>0.0408807357030074</v>
       </c>
       <c r="K40" t="n">
-        <v>0.4350413761493575</v>
+        <v>0.4350413761493574</v>
       </c>
       <c r="L40" t="n">
         <v>0.02241511149442015</v>
@@ -3014,7 +6108,7 @@
         <v>0.2180766949313526</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.411234902349305e-06</v>
+        <v>4.411234902349304e-06</v>
       </c>
       <c r="R40" t="n">
         <v>0.00407448151350845</v>
@@ -3024,6 +6118,84 @@
       </c>
       <c r="T40" t="n">
         <v>0.0032756541480635</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.4995514793736344</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.00044852062636555</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0.0300718837463372</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0.4699281162536628</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/error_models/conv_models/nv_32x8_b1_dat-2097152_wt-131072_int32/unique_complete_df.xlsx
+++ b/error_models/conv_models/nv_32x8_b1_dat-2097152_wt-131072_int32/unique_complete_df.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unique_complete_layers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,307 +425,312 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT40"/>
+  <dimension ref="A1:AV40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Channels_in</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Channels_out</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Input_size</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Kernel_size</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Padding</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Masked</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>SDC</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Crash+Hang</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>FullChannels</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Rectangles</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>SingleChannelRandom</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ShatteredChannel</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>QuasiShatteredChannel</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MultiChannelBlock</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>BulletWake</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>SameRow</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>SingleBlock</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Skip4</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>skip_4-single</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>skip_4-multi</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>single_channel_alternated_blocks-single</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>single_channel_alternated_blocks-multi</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>bullet_wake-single</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>bullet_wake-multi</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>quasi_shattered_channel-single</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>quasi_shattered_channel-multi</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>single_channel_random-single</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>single_channel_random-multi</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>single_block-single</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>single_block-multi</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>same_row-single</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>same_row-multi</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>full_channels-single</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>full_channels-multi</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>multi_channel_block-single</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>multi_channel_block-multi</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>shattered_channel-single</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>shattered_channel-multi</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>multiple_channels_uncategorized-single</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>multiple_channels_uncategorized-multi</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>rectangles-single</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>rectangles-multi</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>single-single</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>single-multi</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv1</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>64</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>32</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>11</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>0.9970608807899808</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.0029315086179794</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>7.552853672781481e-06</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.4648636072535088</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.0934548218002085</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>0.1153476955059989</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>0.0031367254543326</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.115325465795461</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.138387544803009</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.0461304104367934</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>0.0002616013362076</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>2.264089895564424e-07</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>2.668988859357488e-05</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
@@ -739,16 +744,16 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -760,7 +765,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -769,7 +774,7 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -787,110 +792,116 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
         <v>0.0601436519584357</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AT2" t="n">
         <v>0.9398563480415644</v>
       </c>
-      <c r="AS2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv2</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
         <v>64</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>192</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>12</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.9958084185929682</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.0041830522140877</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>8.471454576859035e-06</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.1124122374316609</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.3886565158249144</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0.2253109204430345</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>0.0136723479068469</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.1802254969847332</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.06758443944372031</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>3.460397714944813e-06</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.0001038141473012</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>0.0001951427004715</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.0003571869706927</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0.0002142284678489</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.9993626513702996</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>0.0006373486297004</v>
       </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -908,10 +919,10 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
@@ -929,110 +940,116 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
         <v>0.0601435918536246</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AT3" t="n">
         <v>0.9398564081463754</v>
       </c>
-      <c r="AS3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT3" t="n">
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv3</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" t="n">
         <v>192</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>384</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.9987813375700154</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.001209383284565</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>9.221407052341847e-06</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.050463527273402</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.4946690822711934</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>0.1328826472957329</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0.0326088754049612</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.1981664426551573</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.0660520956573491</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>2.428215122952811e-06</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>0.0220196774140313</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>0.0015976093585685</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0.0015367370048619</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>4.147517436196904e-07</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.999663466259394</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>0.0003365337406058</v>
       </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1050,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1071,110 +1088,116 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
         <v>0.0601436768804276</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AT4" t="n">
         <v>0.9398563231195722</v>
       </c>
-      <c r="AS4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT4" t="n">
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv4</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="D5" t="n">
         <v>384</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>256</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.9978545984675528</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.0021358992802787</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>9.444513801073507e-06</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.0541223292968715</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.455158671003812</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>0.1800080590935711</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>0.0178529547965758</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0.2152886086561792</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.07175874966193679</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>1.616436111796078e-06</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>0.0001843472384303</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>0.0036905310532958</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>0.0003641693370362</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>0.0015695130975847</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.9996603213430532</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>0.0003396786569467</v>
       </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1192,10 +1215,10 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
@@ -1213,110 +1236,116 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
         <v>0.0601436685408916</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AT5" t="n">
         <v>0.9398563314591084</v>
       </c>
-      <c r="AS5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT5" t="n">
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv5</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="D6" t="n">
         <v>256</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>256</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.9986600446913748</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.0013305179158152</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>9.379654442472182e-06</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.0340085967316777</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.4909471405256154</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>0.1821070451799932</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>0.0153981122472452</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.1513813294997633</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.1210911717066233</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>1.328902906021737e-06</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>0.0001342804346129</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>0.0036601215201007</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>1.136056919796271e-05</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.0012590041884596</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.9994935822724006</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>0.0005064177275993</v>
       </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1334,10 +1363,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1355,110 +1384,116 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
         <v>0.0601681476563645</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AT6" t="n">
         <v>0.9398318523436354</v>
       </c>
-      <c r="AS6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>lenet_cifar10_conv1</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="D7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>32</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>32</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
         <v>0.9982699913705976</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.0017211104156602</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>8.840475374939127e-06</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.4470138861534021</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.094203712845013</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>0.1710007931574814</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>0.0026571498160943</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0.1709576842310058</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.0569830257873541</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>2.340838582802788e-06</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.0571432547780089</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>9.092656277876747e-10</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>3.734032878192658e-05</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>7.534166424233711e-07</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1470,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -1479,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1497,110 +1532,116 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
         <v>0.0601437021892878</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AT7" t="n">
         <v>0.939856297810712</v>
       </c>
-      <c r="AS7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT7" t="n">
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>lenet_cifar10_conv2</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="D8" t="n">
         <v>32</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>64</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>16</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>0.9970977859612548</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.0028930214202267</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>9.134880151049476e-06</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.1255357329358054</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.4037921136159926</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>0.1424879904273207</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>0.0136738566387342</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.1519642135378255</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.07597901067714639</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>4.253559696359573e-06</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.0666042674777126</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>0.0095295632083816</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>0.0003449254323903</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>0.0100835246752953</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1618,10 +1659,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
@@ -1639,90 +1680,96 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
         <v>0.0601436574782959</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AT8" t="n">
         <v>0.939856342521704</v>
       </c>
-      <c r="AS8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.1.conv.1</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="D9" t="n">
         <v>32</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>16</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>16</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>0.9990668387669625</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.0009228714420521</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>1.023205261822674e-05</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.2947113784351706</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.253821981048511</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>0.0002748793410555</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>9.233707821064235e-06</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>7.612274742402022e-06</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.451059284422834</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>2.210179672393788e-05</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>8.049148423246839e-05</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>1.29797505415866e-05</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
@@ -1733,16 +1780,16 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1760,10 +1807,10 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1781,84 +1828,90 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ9" t="n">
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.10.conv.2</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="D10" t="n">
         <v>384</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>64</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>8</v>
       </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.999313614435163</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.0006767087781422</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>9.619048327502796e-06</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.0298173449191854</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.6943142479215995</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>0.003629834930049</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>6.850169069466317e-06</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>9.991396525170324e-09</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>0.2691323742833849</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>0.0030992800469478</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
@@ -1875,55 +1928,55 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ10" t="n">
         <v>0</v>
@@ -1932,75 +1985,81 @@
         <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.12.conv.0.0</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="D11" t="n">
         <v>96</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>576</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>8</v>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.9997664361131036</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.000224725320906</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>8.780827622820686e-06</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.0002227903915923</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.7574305245336851</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>2.323273162441621e-05</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>0.09689928740602829</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>0.1453257695459612</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>9.833765274137056e-05</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
@@ -2017,55 +2076,55 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ11" t="n">
         <v>0</v>
@@ -2074,81 +2133,87 @@
         <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.2.conv.2</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="D12" t="n">
         <v>96</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>24</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>8</v>
       </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
       <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>0.9987654669291792</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.0012243180101789</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>1.015732227458142e-05</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.1430071878886577</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>0.0130998700625371</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>4.224206300476753e-06</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.366516410840334</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.4643416609162749</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>6.323823887077222e-05</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.0113505049500716</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.0016168451585859</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
@@ -2159,16 +2224,16 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2186,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2207,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ12" t="n">
         <v>0</v>
@@ -2216,81 +2281,87 @@
         <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.3.conv.0.0</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="D13" t="n">
         <v>24</v>
       </c>
-      <c r="C13" t="n">
+      <c r="E13" t="n">
         <v>144</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>8</v>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.9997204261302196</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.0002700638715348</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>9.452259878412959e-06</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.0728795669553698</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>8.258495783586163e-07</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>0.0001316435726403</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>6.416516748309673e-06</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>0.6181417919575423</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>0.3083672200957901</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>5.368966093943221e-05</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>0.0004130067059755</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
         <v>5.78094704851046e-06</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
@@ -2301,16 +2372,16 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2328,10 +2399,10 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2349,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ13" t="n">
         <v>0</v>
@@ -2358,81 +2429,87 @@
         <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.3.conv.2</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="D14" t="n">
         <v>144</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>24</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>0.9984088207119576</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.0015807185049269</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>1.04030447482993e-05</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.0411196101622397</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>0.0189692376880263</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>4.662025762063601e-06</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>0.4601994689767856</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.4678026221990511</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>0.0012303785389429</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.0106580718350726</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>1.589083575221068e-05</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
@@ -2443,16 +2520,16 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2470,10 +2547,10 @@
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2491,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
@@ -2500,81 +2577,87 @@
         <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.4.conv.0.0</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="D15" t="n">
         <v>24</v>
       </c>
-      <c r="C15" t="n">
+      <c r="E15" t="n">
         <v>144</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>0.999783363530822</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.0002066441911791</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>9.934539631584196e-06</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.1213874853371758</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>0.0001168293003996</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>6.618608702659462e-06</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.678145359376344</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.1937961791351622</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>5.950679067492405e-05</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.006481786569632</v>
       </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
         <v>6.177143541326481e-06</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
@@ -2585,16 +2668,16 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2612,10 +2695,10 @@
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2633,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ15" t="n">
         <v>0</v>
@@ -2642,81 +2725,87 @@
         <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.5.conv.0.0</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="D16" t="n">
         <v>32</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
         <v>192</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>4</v>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
       <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>0.9999035124624248</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>8.75422575093377e-05</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>8.88754169859135e-06</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.0486491909560327</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>6.115087683324124e-05</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>1.689076597423893e-06</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>0.0001702024490114</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>1.116824354729496e-05</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.8853264896345083</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.0485760521944168</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>8.689512631814093e-05</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.0171104305542195</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>6.673150147527908e-06</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
@@ -2727,16 +2816,16 @@
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2754,10 +2843,10 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2775,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ16" t="n">
         <v>0</v>
@@ -2784,83 +2873,89 @@
         <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.5.conv.2</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="D17" t="n">
         <v>192</v>
       </c>
-      <c r="C17" t="n">
+      <c r="E17" t="n">
         <v>32</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>0.9990745967760062</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.0009152389484001</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>1.010653722632491e-05</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.0523884603054125</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.0023129292185213</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>5.25771214671531e-06</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>0.016190434629397</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>9.154790825230074e-06</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>5.721966221132586e-09</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>0.5168139047182773</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.4037252981315248</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>0.0023666650344628</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>0.0038450644791221</v>
       </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
         <v>0.0023427675199765</v>
       </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -2869,16 +2964,16 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2896,10 +2991,10 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2917,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ17" t="n">
         <v>0</v>
@@ -2926,81 +3021,87 @@
         <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.6.conv.0.0</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="D18" t="n">
         <v>32</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
         <v>192</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>2</v>
       </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>0.9998530210218576</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>0.0001377829422603</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>9.138297514923172e-06</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.0244116404317717</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>7.3744878436812e-05</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>8.441376226346062e-07</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>0.0001769332598197</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>1.18051118585936e-05</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.7724074120940126</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.1938961639766374</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>8.788293252654059e-05</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.0089212857845959</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>1.222965435045942e-05</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
@@ -3011,16 +3112,16 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3038,10 +3139,10 @@
         <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3059,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ18" t="n">
         <v>0</v>
@@ -3068,75 +3169,81 @@
         <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.7.conv.2</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="D19" t="n">
         <v>192</v>
       </c>
-      <c r="C19" t="n">
+      <c r="E19" t="n">
         <v>64</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>0.9997373751990491</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.0002532161692565</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>9.350893326923242e-06</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.0016607488133891</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.892790436610077</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.001468088852212</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>6.881970274562899e-06</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>5.223383823596383e-09</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.0969333181910812</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>0.0071404626012148</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
@@ -3153,55 +3260,55 @@
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM19" t="n">
         <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ19" t="n">
         <v>0</v>
@@ -3210,75 +3317,81 @@
         <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.8.conv.0.0</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="D20" t="n">
         <v>64</v>
       </c>
-      <c r="C20" t="n">
+      <c r="E20" t="n">
         <v>384</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>2</v>
       </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
       <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>0.9998337695445598</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>0.000157705143853</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>8.467573219811256e-06</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.0035609744190337</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.9322529162707092</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>0.0034057747785133</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>5.093942775876544e-06</v>
       </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
       <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>0.0606834292420469</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>9.175360855344565e-05</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
@@ -3295,55 +3408,55 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM20" t="n">
         <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ20" t="n">
         <v>0</v>
@@ -3352,75 +3465,81 @@
         <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.9.conv.2</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="D21" t="n">
         <v>384</v>
       </c>
-      <c r="C21" t="n">
+      <c r="E21" t="n">
         <v>64</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>2</v>
       </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
       <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>0.9993693428760536</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.0006207443097648</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>9.855075814226207e-06</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.0068405302047322</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.7415270581602458</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.0065824141604693</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>7.094168502526982e-06</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>1.844213572839163e-08</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>0.2422190543027995</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>0.0028237728227474</v>
       </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
@@ -3437,55 +3556,55 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM21" t="n">
         <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ21" t="n">
         <v>0</v>
@@ -3494,72 +3613,78 @@
         <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>res50_cifar10_layer1.2.conv1</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="D22" t="n">
         <v>256</v>
       </c>
-      <c r="C22" t="n">
+      <c r="E22" t="n">
         <v>64</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>32</v>
       </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
       <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>0.4564744900633816</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.5435147420935058</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>1.071010474527647e-05</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.0010540686188921</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.989983381477447</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>2.406212891098098e-06</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>2.658717014114385e-08</v>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
       <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>0.0089600593652323</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
@@ -3579,13 +3704,13 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3609,25 +3734,25 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM22" t="n">
         <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ22" t="n">
         <v>0</v>
@@ -3639,78 +3764,84 @@
         <v>0</v>
       </c>
       <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>res50_cifar10_layer2.1.conv1</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="D23" t="n">
         <v>512</v>
       </c>
-      <c r="C23" t="n">
+      <c r="E23" t="n">
         <v>128</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>16</v>
       </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
       <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>0.5616201945443819</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.4383692522533035</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>1.049546394736786e-05</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.2814178060244685</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.7155284001246497</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
         <v>0.0004722113031273</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>4.126026959249102e-06</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
         <v>2.765769221347636e-06</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>0.0025327827179258</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>1.948515200243556e-05</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>1.835415390976763e-05</v>
       </c>
-      <c r="T23" t="n">
+      <c r="V23" t="n">
         <v>4.010989368309911e-06</v>
       </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
@@ -3721,16 +3852,16 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3748,10 +3879,10 @@
         <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3769,90 +3900,96 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ23" t="n">
         <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>res50_cifar10_layer3.0.conv3</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="D24" t="n">
         <v>256</v>
       </c>
-      <c r="C24" t="n">
+      <c r="E24" t="n">
         <v>1024</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>8</v>
       </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
       <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>0.9970674086289752</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.0029221006881305</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>1.043294452696141e-05</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.042651307326255</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.0234889284775353</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>3.833915642672003e-06</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
         <v>0.4602084103775065</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>0.4662867010830588</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>4.45720564446589e-05</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.0059405706503547</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>0.0013756183748347</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
@@ -3863,16 +4000,16 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3890,10 +4027,10 @@
         <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3911,7 +4048,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ24" t="n">
         <v>0</v>
@@ -3920,83 +4057,89 @@
         <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>res50_cifar10_layer4.1.conv3</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="D25" t="n">
         <v>512</v>
       </c>
-      <c r="C25" t="n">
+      <c r="E25" t="n">
         <v>2048</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>4</v>
       </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
       <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>0.9980202385980472</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.0019691327124607</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>1.057095112492609e-05</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.0169757817536677</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.0021315836377223</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>0.0002399680227117</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>0.020757914627783</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>6.507487233425274e-06</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>8.773050146552966e-10</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>0.4844898315154882</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>0.468895793624038</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>0.0017477600082211</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0.0021275352084985</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>0.0026272654989634</v>
       </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -4005,16 +4148,16 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -4032,10 +4175,10 @@
         <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4053,10 +4196,10 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
         <v>0</v>
@@ -4065,98 +4208,104 @@
         <v>1</v>
       </c>
       <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.11</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="D26" t="n">
         <v>256</v>
       </c>
-      <c r="C26" t="n">
+      <c r="E26" t="n">
         <v>512</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>16</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>3</v>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
         <v>0.9985867064411492</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.0014036324354832</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>9.603385000067223e-06</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.0267175018534994</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.0039800180779861</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>0.0505593746013186</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>0.0139294842275575</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>0.2421934407031534</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.09687280533227199</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>0.5087678039407761</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>2.189971439449085e-05</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>0.0029967427061979</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>0.0031601249203583</v>
       </c>
-      <c r="T26" t="n">
+      <c r="V26" t="n">
         <v>0.0508003363117567</v>
       </c>
-      <c r="U26" t="n">
+      <c r="W26" t="n">
         <v>0.9991002517197236</v>
       </c>
-      <c r="V26" t="n">
+      <c r="X26" t="n">
         <v>0.0008997482802761</v>
       </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
       <c r="Y26" t="n">
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -4174,10 +4323,10 @@
         <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4195,110 +4344,116 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
         <v>0.0601437703608389</v>
       </c>
-      <c r="AR26" t="n">
+      <c r="AT26" t="n">
         <v>0.9398562296391612</v>
       </c>
-      <c r="AS26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT26" t="n">
+      <c r="AU26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.3</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="D27" t="n">
         <v>64</v>
       </c>
-      <c r="C27" t="n">
+      <c r="E27" t="n">
         <v>128</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>4</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>3</v>
       </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
         <v>0.9956601312862088</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.0043309647984937</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>8.846176930220794e-06</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.1766009540074539</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.3303512753701568</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>0.1773973244943814</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>0.0145276413596053</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>0.1637339864300899</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.0682205949987074</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>3.70929994048731e-06</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>0.0342252344453126</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>0.0069988441633688</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>5.714540089467125e-05</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
         <v>0.0210608290471515</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4316,10 +4471,10 @@
         <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4337,110 +4492,116 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
         <v>0.0601436798342393</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AT27" t="n">
         <v>0.9398563201657608</v>
       </c>
-      <c r="AS27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT27" t="n">
+      <c r="AU27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV27" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.6</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="D28" t="n">
         <v>128</v>
       </c>
-      <c r="C28" t="n">
+      <c r="E28" t="n">
         <v>256</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>2</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>3</v>
       </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
         <v>0.9976654385627982</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>0.0023256186455008</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>8.885053333630302e-06</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.0490022766589829</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0.1908344589773623</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>0.0137918693760886</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>0.1467884438518951</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.0880680331774318</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>0.4360487141219951</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>0.0294052849518392</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>6.391545110847295e-05</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>0.0162416924662246</v>
       </c>
-      <c r="T28" t="n">
+      <c r="V28" t="n">
         <v>0.0150773603444507</v>
       </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4458,10 +4619,10 @@
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4479,110 +4640,116 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ28" t="n">
         <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.8</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="D29" t="n">
         <v>256</v>
       </c>
-      <c r="C29" t="n">
+      <c r="E29" t="n">
         <v>256</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>2</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>3</v>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
         <v>0.9956459757812586</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.0043448240344406</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>9.142445933243638e-06</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.0020976056137648</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0.2248940806982216</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>0.0316389851792975</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>0.1643453335363472</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.0432486233717434</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>0.4845240504811791</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>0.0173365716308662</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>0.0021876355713428</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0.001610883397524</v>
       </c>
-      <c r="T29" t="n">
+      <c r="V29" t="n">
         <v>0.02811592477762</v>
       </c>
-      <c r="U29" t="n">
+      <c r="W29" t="n">
         <v>0.0588223645662031</v>
       </c>
-      <c r="V29" t="n">
+      <c r="X29" t="n">
         <v>0.9411776354337968</v>
       </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
       <c r="Y29" t="n">
         <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4600,10 +4767,10 @@
         <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4621,87 +4788,93 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ29" t="n">
         <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer2.0.conv1</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="D30" t="n">
         <v>256</v>
       </c>
-      <c r="C30" t="n">
+      <c r="E30" t="n">
         <v>128</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>32</v>
       </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
       <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>0.4606602081376381</v>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>0.539329862301924</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>9.87182207061686e-06</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.0002689858061431</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.9928283591874356</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>1.600596862365807e-06</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>9.621947463518597e-07</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
         <v>1.379929081096008e-08</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>0.0069000201723381</v>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
         <v>5.048163266842828e-10</v>
       </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
@@ -4715,13 +4888,13 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4745,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4763,7 +4936,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ30" t="n">
         <v>0</v>
@@ -4775,78 +4948,84 @@
         <v>0</v>
       </c>
       <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer2.3.conv3</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="D31" t="n">
         <v>128</v>
       </c>
-      <c r="C31" t="n">
+      <c r="E31" t="n">
         <v>512</v>
       </c>
-      <c r="D31" t="n">
+      <c r="F31" t="n">
         <v>16</v>
       </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
       <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
         <v>0.9947351703719656</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>0.005253846996312</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>1.092489335516587e-05</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>0.162184380919582</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.3875362469370294</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>0.0293478115531959</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>8.023497713924495e-06</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>1.375890722956771e-07</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>4.2999956750168e-06</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>0.4208819039687843</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>1.806059206932854e-05</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>6.03633448988575e-06</v>
       </c>
-      <c r="T31" t="n">
+      <c r="V31" t="n">
         <v>1.304087402059125e-05</v>
       </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
       <c r="W31" t="n">
         <v>0</v>
       </c>
@@ -4857,16 +5036,16 @@
         <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4884,10 +5063,10 @@
         <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
         <v>0</v>
@@ -4905,90 +5084,96 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ31" t="n">
         <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer3.0.conv3</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="D32" t="n">
         <v>256</v>
       </c>
-      <c r="C32" t="n">
+      <c r="E32" t="n">
         <v>1024</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>16</v>
       </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
       <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>0.5352000290055247</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.4647881069812706</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>1.180627483744562e-05</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>0.1123738031484516</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.8853860979634317</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>2.903368045537756e-08</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>0.0005205898049269</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>5.215138425480357e-05</v>
       </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
         <v>2.995106395590484e-06</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>0.0015990697977935</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>1.879962857876022e-05</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>4.600646585855962e-05</v>
       </c>
-      <c r="T32" t="n">
+      <c r="V32" t="n">
         <v>3.999282607512221e-07</v>
       </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
       <c r="W32" t="n">
         <v>0</v>
       </c>
@@ -4999,16 +5184,16 @@
         <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -5026,10 +5211,10 @@
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
@@ -5047,110 +5232,116 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ32" t="n">
         <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer3.1.conv2</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="D33" t="n">
         <v>256</v>
       </c>
-      <c r="C33" t="n">
+      <c r="E33" t="n">
         <v>256</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>16</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>3</v>
       </c>
-      <c r="F33" t="n">
+      <c r="H33" t="n">
         <v>2</v>
       </c>
-      <c r="G33" t="n">
+      <c r="I33" t="n">
         <v>0.5394700223404187</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.4605216259256646</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>8.293995549455326e-06</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.2092905055481372</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.7890436087162528</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>5.75644312779009e-07</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>0.0004682294187659</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>0.0007187974929619</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>0.0002823525682916</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>3.089507817591533e-06</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>2.840485962245005e-05</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>2.338588469067316e-05</v>
       </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
         <v>1.522227391643169e-05</v>
       </c>
-      <c r="T33" t="n">
+      <c r="V33" t="n">
         <v>0.0001248184384666</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
       <c r="W33" t="n">
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -5168,10 +5359,10 @@
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
         <v>0</v>
@@ -5189,72 +5380,78 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ33" t="n">
         <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer4.0.conv2</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="D34" t="n">
         <v>512</v>
       </c>
-      <c r="C34" t="n">
+      <c r="E34" t="n">
         <v>512</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>16</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>3</v>
       </c>
-      <c r="F34" t="n">
+      <c r="H34" t="n">
         <v>2</v>
       </c>
-      <c r="G34" t="n">
+      <c r="I34" t="n">
         <v>0.3899910008940899</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.6100006531783309</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>8.288189212092459e-06</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>0.9959923245526228</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>0.0001814477511417</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>0.0035225056754977</v>
       </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
@@ -5265,19 +5462,19 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
         <v>0.0003036642823704</v>
       </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1</v>
-      </c>
       <c r="W34" t="n">
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -5292,13 +5489,13 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -5313,25 +5510,25 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
         <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM34" t="n">
         <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ34" t="n">
         <v>0</v>
@@ -5343,98 +5540,104 @@
         <v>0</v>
       </c>
       <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>merge0</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="D35" t="n">
         <v>3</v>
       </c>
-      <c r="C35" t="n">
+      <c r="E35" t="n">
         <v>64</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>32</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>3</v>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
         <v>0.9977487239418743</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.00224321916395075</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>7.999155807480883e-06</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.2606754565978011</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.4499786304950936</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>0.06926174671220156</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>0.0035288322122176</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>0.06920471523077361</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>0.08216708836778325</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>2.428341118265331e-06</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
         <v>0.04787173368065545</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>1.741618169187343e-06</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>8.711188211706547e-06</v>
       </c>
-      <c r="T35" t="n">
+      <c r="V35" t="n">
         <v>0.01729885781760712</v>
       </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1</v>
-      </c>
       <c r="W35" t="n">
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5446,7 +5649,7 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH35" t="n">
         <v>0</v>
@@ -5455,7 +5658,7 @@
         <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
         <v>0</v>
@@ -5473,116 +5676,122 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
         <v>0.0308187601353429</v>
       </c>
-      <c r="AR35" t="n">
+      <c r="AT35" t="n">
         <v>0.969181239864657</v>
       </c>
-      <c r="AS35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT35" t="n">
+      <c r="AU35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV35" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>merge1</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="D36" t="n">
         <v>64</v>
       </c>
-      <c r="C36" t="n">
+      <c r="E36" t="n">
         <v>64</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>32</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>3</v>
       </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
         <v>0.3780880368360491</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.6219037809836955</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>8.12444188804311e-06</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.0002692842159856</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.9970322622341365</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>0.00080360329987875</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>1.879557045826975e-05</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>0.00107080389863105</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>0.00080248628578265</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>4.64967009978867e-08</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>1.850651466954503e-06</v>
       </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
         <v>7.985375985510407e-07</v>
       </c>
-      <c r="T36" t="n">
+      <c r="V36" t="n">
         <v>1.107099283099145e-08</v>
       </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1</v>
-      </c>
       <c r="W36" t="n">
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -5597,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
         <v>0</v>
@@ -5615,110 +5824,116 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ36" t="n">
         <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>35</v>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>merge2</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="D37" t="n">
         <v>128</v>
       </c>
-      <c r="C37" t="n">
+      <c r="E37" t="n">
         <v>128</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>16</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>3</v>
       </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
         <v>0.9913463127406167</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.0086446721123025</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>8.957408713475789e-06</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.1644756318087491</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.3370305698800756</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>0.2736151025963407</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>0.0260178090478567</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>0.1238022507279324</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>0.0475202979169005</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>3.39657994025975e-06</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>0.01426147629070385</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>0.002334833196578907</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
         <v>5.428273740503373e-05</v>
       </c>
-      <c r="T37" t="n">
+      <c r="V37" t="n">
         <v>0.0067926380532664</v>
       </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1</v>
-      </c>
       <c r="W37" t="n">
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5736,10 +5951,10 @@
         <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
         <v>0</v>
@@ -5757,110 +5972,116 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
         <v>6.91173154459638e-09</v>
       </c>
-      <c r="AR37" t="n">
+      <c r="AT37" t="n">
         <v>0.9999999930882684</v>
       </c>
-      <c r="AS37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT37" t="n">
+      <c r="AU37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>merge3</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="D38" t="n">
         <v>256</v>
       </c>
-      <c r="C38" t="n">
+      <c r="E38" t="n">
         <v>256</v>
       </c>
-      <c r="D38" t="n">
+      <c r="F38" t="n">
         <v>8</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>3</v>
       </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
         <v>0.9930947811703106</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.006896132347495851</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>9.028743826126227e-06</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>0.07696419881105945</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>0.2252948560306084</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>0.0264454888558836</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>0.1875785409766181</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>0.0359818849142691</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>0.4119023086519705</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
         <v>0.007185520911252644</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>0.0002955708877883</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>0.002787547919661</v>
       </c>
-      <c r="T38" t="n">
+      <c r="V38" t="n">
         <v>0.00383033473021645</v>
       </c>
-      <c r="U38" t="n">
+      <c r="W38" t="n">
         <v>0.9994576959775634</v>
       </c>
-      <c r="V38" t="n">
+      <c r="X38" t="n">
         <v>0.0005423040224364</v>
       </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
       <c r="Y38" t="n">
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5878,10 +6099,10 @@
         <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
         <v>0</v>
@@ -5899,302 +6120,320 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ38" t="n">
         <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>merge4</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="D39" t="n">
         <v>512</v>
       </c>
-      <c r="C39" t="n">
+      <c r="E39" t="n">
         <v>512</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>4</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>3</v>
       </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
         <v>0.9965936541039709</v>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>0.003396805378778325</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>9.482778883366627e-06</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.02605461004909563</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.2272696663123775</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>0.03456404672940765</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>0.0112784094056993</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>0.250675983365741</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>0.06329042253880036</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>0.3699561479226838</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>1.996382813267721e-05</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>0.004036656959353325</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.0002094480522284675</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.00333015666035385</v>
       </c>
-      <c r="U39" t="n">
+      <c r="W39" t="n">
         <v>0.7494389442717997</v>
       </c>
-      <c r="V39" t="n">
+      <c r="X39" t="n">
         <v>0.00056105572820025</v>
       </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
       <c r="Y39" t="n">
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
       </c>
       <c r="AE39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
         <v>0.75</v>
       </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1</v>
-      </c>
       <c r="AH39" t="n">
         <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
         <v>0</v>
       </c>
       <c r="AL39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
         <v>0.75</v>
       </c>
-      <c r="AM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1</v>
-      </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
         <v>0.04510783172555782</v>
       </c>
-      <c r="AR39" t="n">
+      <c r="AT39" t="n">
         <v>0.7048921682744422</v>
       </c>
-      <c r="AS39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT39" t="n">
+      <c r="AU39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>38</v>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>merge5</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="D40" t="n">
         <v>512</v>
       </c>
-      <c r="C40" t="n">
+      <c r="E40" t="n">
         <v>512</v>
       </c>
-      <c r="D40" t="n">
+      <c r="F40" t="n">
         <v>8</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
         <v>3</v>
       </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
         <v>0.9986247528817271</v>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>0.0013656784984827</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>9.510881422999171e-06</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>0.0408807357030074</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>0.4350413761493574</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>0.02241511149442015</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>0.006473950156132949</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>0.1522918959247535</v>
       </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
         <v>0.1174203244345728</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>0.2180766949313526</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
         <v>4.411234902349304e-06</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>0.00407448151350845</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>4.515434995533196e-05</v>
       </c>
-      <c r="T40" t="n">
+      <c r="V40" t="n">
         <v>0.0032756541480635</v>
       </c>
-      <c r="U40" t="n">
+      <c r="W40" t="n">
         <v>0.4995514793736344</v>
       </c>
-      <c r="V40" t="n">
+      <c r="X40" t="n">
         <v>0.00044852062636555</v>
       </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
       <c r="Y40" t="n">
         <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
       </c>
       <c r="AE40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1</v>
-      </c>
       <c r="AH40" t="n">
         <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
       </c>
       <c r="AL40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AM40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>1</v>
-      </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
         <v>0.0300718837463372</v>
       </c>
-      <c r="AR40" t="n">
+      <c r="AT40" t="n">
         <v>0.4699281162536628</v>
       </c>
-      <c r="AS40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT40" t="n">
+      <c r="AU40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV40" t="n">
         <v>0</v>
       </c>
     </row>
